--- a/output/stock_quant_scores/BATS.L_balance_df.xlsx
+++ b/output/stock_quant_scores/BATS.L_balance_df.xlsx
@@ -1725,25 +1725,35 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>39658000000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>-2337000000</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>67101000000</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>49334000000</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>69964000000</v>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1753,7 +1763,9 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>15144000000</v>
+      </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
@@ -1761,7 +1773,9 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
+      <c r="AP6" t="n">
+        <v>137365000000</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
@@ -1784,18 +1798,24 @@
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>12807000000</v>
+      </c>
       <c r="BL6" t="inlineStr"/>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>5279000000</v>
+      </c>
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
+      <c r="BV6" t="n">
+        <v>1480000000</v>
+      </c>
       <c r="BW6" t="inlineStr"/>
       <c r="BX6" t="inlineStr"/>
     </row>
